--- a/TEngine/Configs/GameConfig/Datas/Language.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Language.xlsx
@@ -575,7 +575,7 @@
     <t>I cleared level {0}! How far can you get?</t>
   </si>
   <si>
-    <t>FeiHuaSongTi-2</t>
+    <t>GeourceSansCHS-Medium</t>
   </si>
   <si>
     <t>sudoku_text_001</t>
@@ -1473,7 +1473,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
@@ -1500,6 +1500,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="差" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2002,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AA161"/>
+  <dimension ref="A1:AA197"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="27.375" bestFit="1" customWidth="1"/>
@@ -4241,6 +4244,798 @@
         </is>
       </c>
     </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_trophy_hall</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-奖杯馆</t>
+        </is>
+      </c>
+      <c r="D162" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆</t>
+        </is>
+      </c>
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trophy Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.2" ht="28.5" customHeight="1">
+      <c r="B163" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_monthly_trophy</t>
+        </is>
+      </c>
+      <c r="C163" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-月度奖杯</t>
+        </is>
+      </c>
+      <c r="D163" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本月奖杯</t>
+        </is>
+      </c>
+      <c r="E163" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This Month's Trophy</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_trophy_leo</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-狮子奖杯</t>
+        </is>
+      </c>
+      <c r="D164" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狮子之杯</t>
+        </is>
+      </c>
+      <c r="E164" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leo Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.2" ht="42.75" customHeight="1">
+      <c r="B165" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_trophy_unlock_desc</t>
+        </is>
+      </c>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-领奖说明</t>
+        </is>
+      </c>
+      <c r="D165" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成本月全部挑战即可获得</t>
+        </is>
+      </c>
+      <c r="E165" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete all challenges this month to earn it</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_calendar_month</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-年/月</t>
+        </is>
+      </c>
+      <c r="D166" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}年{1}月</t>
+        </is>
+      </c>
+      <c r="E166" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1}/{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_monday</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周一</t>
+        </is>
+      </c>
+      <c r="D167" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一</t>
+        </is>
+      </c>
+      <c r="E167" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mon</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_tuesday</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周二</t>
+        </is>
+      </c>
+      <c r="D168" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">二</t>
+        </is>
+      </c>
+      <c r="E168" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tue</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_wednesday</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周三</t>
+        </is>
+      </c>
+      <c r="D169" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三</t>
+        </is>
+      </c>
+      <c r="E169" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wed</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_thursday</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周四</t>
+        </is>
+      </c>
+      <c r="D170" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">四</t>
+        </is>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thu</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_friday</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周五</t>
+        </is>
+      </c>
+      <c r="D171" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">五</t>
+        </is>
+      </c>
+      <c r="E171" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_saturday</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周六</t>
+        </is>
+      </c>
+      <c r="D172" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">六</t>
+        </is>
+      </c>
+      <c r="E172" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sat</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_weekday_sunday</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-周日</t>
+        </is>
+      </c>
+      <c r="D173" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日</t>
+        </is>
+      </c>
+      <c r="E173" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sun</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_selected_info</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-月/日/难度</t>
+        </is>
+      </c>
+      <c r="D174" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}月{1}日 · {2}</t>
+        </is>
+      </c>
+      <c r="E174" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}/{1} · {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.2" ht="14.25" customHeight="1">
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_progress</t>
+        </is>
+      </c>
+      <c r="C175" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-百分比</t>
+        </is>
+      </c>
+      <c r="D175" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 {0}%</t>
+        </is>
+      </c>
+      <c r="E175" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress {0}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.2" ht="28.5" customHeight="1">
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">daily_continue_today</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每日挑战-继续按钮</t>
+        </is>
+      </c>
+      <c r="D176" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">继续今日挑战</t>
+        </is>
+      </c>
+      <c r="E176" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continue Today's Challenge</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="32" customHeight="1">
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_year</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-年份</t>
+        </is>
+      </c>
+      <c r="D177" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}年</t>
+        </is>
+      </c>
+      <c r="E177" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="32" customHeight="1">
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_collected</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-年度收集数量</t>
+        </is>
+      </c>
+      <c r="D178" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已收集 {0} / {1}</t>
+        </is>
+      </c>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Collected {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="76" customHeight="1">
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_gallery_desc</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-说明</t>
+        </is>
+      </c>
+      <c r="D179" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">完成整月每日挑战，收藏当月星座奖杯</t>
+        </is>
+      </c>
+      <c r="E179" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Complete every daily challenge in a month to collect its zodiac trophy</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="32" customHeight="1">
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_month_name</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-月份和名称</t>
+        </is>
+      </c>
+      <c r="D180" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{0}月 · {1}</t>
+        </is>
+      </c>
+      <c r="E180" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Month {0} · {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="32" customHeight="1">
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_obtained</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-已获得</t>
+        </is>
+      </c>
+      <c r="D181" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已获得</t>
+        </is>
+      </c>
+      <c r="E181" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Obtained</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="32" customHeight="1">
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_not_obtained</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-未获得</t>
+        </is>
+      </c>
+      <c r="D182" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">未获得</t>
+        </is>
+      </c>
+      <c r="E182" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Obtained</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="32" customHeight="1">
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_not_started</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-待开启</t>
+        </is>
+      </c>
+      <c r="D183" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">待开启</t>
+        </is>
+      </c>
+      <c r="E183" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coming Soon</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="32" customHeight="1">
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_progress</t>
+        </is>
+      </c>
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-月度完成数量</t>
+        </is>
+      </c>
+      <c r="D184" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">进行中 {0}/{1}</t>
+        </is>
+      </c>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">In Progress {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="76" customHeight="1">
+      <c r="B185" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_gallery_footer</t>
+        </is>
+      </c>
+      <c r="C185" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-底部说明</t>
+        </is>
+      </c>
+      <c r="D185" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">每月一款，记录你的坚持</t>
+        </is>
+      </c>
+      <c r="E185" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A trophy each month to celebrate your dedication</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="32" customHeight="1">
+      <c r="B186" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_capricorn</t>
+        </is>
+      </c>
+      <c r="C186" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D186" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">摩羯</t>
+        </is>
+      </c>
+      <c r="E186" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capricorn</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="32" customHeight="1">
+      <c r="B187" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_aquarius</t>
+        </is>
+      </c>
+      <c r="C187" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D187" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">水瓶</t>
+        </is>
+      </c>
+      <c r="E187" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aquarius</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="32" customHeight="1">
+      <c r="B188" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_pisces</t>
+        </is>
+      </c>
+      <c r="C188" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D188" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双鱼</t>
+        </is>
+      </c>
+      <c r="E188" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pisces</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="32" customHeight="1">
+      <c r="B189" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_aries</t>
+        </is>
+      </c>
+      <c r="C189" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D189" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白羊</t>
+        </is>
+      </c>
+      <c r="E189" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aries</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="32" customHeight="1">
+      <c r="B190" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_taurus</t>
+        </is>
+      </c>
+      <c r="C190" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D190" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金牛</t>
+        </is>
+      </c>
+      <c r="E190" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taurus</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="32" customHeight="1">
+      <c r="B191" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_gemini</t>
+        </is>
+      </c>
+      <c r="C191" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D191" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">双子</t>
+        </is>
+      </c>
+      <c r="E191" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gemini</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="32" customHeight="1">
+      <c r="B192" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_cancer</t>
+        </is>
+      </c>
+      <c r="C192" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D192" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">巨蟹</t>
+        </is>
+      </c>
+      <c r="E192" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cancer</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="32" customHeight="1">
+      <c r="B193" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_leo</t>
+        </is>
+      </c>
+      <c r="C193" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D193" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">狮子</t>
+        </is>
+      </c>
+      <c r="E193" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leo</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="32" customHeight="1">
+      <c r="B194" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_virgo</t>
+        </is>
+      </c>
+      <c r="C194" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D194" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">处女</t>
+        </is>
+      </c>
+      <c r="E194" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Virgo</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="32" customHeight="1">
+      <c r="B195" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_libra</t>
+        </is>
+      </c>
+      <c r="C195" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D195" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天秤</t>
+        </is>
+      </c>
+      <c r="E195" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Libra</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="32" customHeight="1">
+      <c r="B196" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_scorpio</t>
+        </is>
+      </c>
+      <c r="C196" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D196" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天蝎</t>
+        </is>
+      </c>
+      <c r="E196" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scorpio</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="32" customHeight="1">
+      <c r="B197" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">trophy_zodiac_sagittarius</t>
+        </is>
+      </c>
+      <c r="C197" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">奖杯馆-星座名称</t>
+        </is>
+      </c>
+      <c r="D197" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">射手</t>
+        </is>
+      </c>
+      <c r="E197" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sagittarius</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="D1:E1"/>
